--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:46</t>
+    <t xml:space="preserve">2026-09-09 23:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:45</t>
+    <t xml:space="preserve">2026-09-18 10:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:34</t>
+    <t xml:space="preserve">2026-09-23 13:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 13:06</t>
+    <t xml:space="preserve">2026-10-02 15:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:21</t>
+    <t xml:space="preserve">2026-10-05 13:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -891,7 +891,7 @@
         <v>2020</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>114089.62</v>
+        <v>114089.63</v>
       </c>
     </row>
     <row r="22">
